--- a/customer_satisfaction_evaluation_forms/043_migration_feedback_form--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/043_migration_feedback_form--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>customer_satisfaction_rating</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>customer_satisfaction_evaluation_form</t>
+          <t>Customer Satisfaction Rating</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>migration_experience</t>
+          <t>customer_satisfaction_comment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>migration_experience</t>
+          <t>Customer Satisfaction Comment</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>feedback_score</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feedback_score</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>attached_file</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>Attached File</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>migration_date</t>
+          <t>Migration Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>migration_time</t>
+          <t>Migration Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,69 +653,69 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>migration_type</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Migration Type</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>migration_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Migration Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>customer_satisfaction</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Customer Satisfaction</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>assigned_user</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>assigned_user</t>
+          <t>Submitted By</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>migration_id</t>
+          <t>migrated_by</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>migration_id</t>
+          <t>Migrated By</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>customer_satisfaction</t>
+          <t>migration_notes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>customer_satisfaction</t>
+          <t>Migration Notes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>attached_files</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Attached Files</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,23 +837,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>customer_satisfaction_rating_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Customer Satisfaction Rating 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>attached_file</t>
+          <t>customer_satisfaction_comment_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>attached_file</t>
+          <t>Customer Satisfaction Comment 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>migration_type</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>migration_type</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,274 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>migration_status</t>
+          <t>attached_file_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>migration_status</t>
+          <t>Attached File 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>migration_notes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>migration_notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>attached_file</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>attached_file</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_rating</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_rating</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_comment</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_comment</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>attached_files</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>attached_files</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>migrated_by</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>migrated_by</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>migration_date</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>migration_date</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>migrated_at</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>migrated_at</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>migration_type</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>migration_type</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1190,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1218,85 +965,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_satisfaction_choices</t>
+          <t>customer_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>five_stars</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Five Stars</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_satisfaction_choices</t>
+          <t>customer_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>four_stars</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Four Stars</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_satisfaction_choices</t>
+          <t>customer_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>three_stars</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Three Stars</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_satisfaction_choices</t>
+          <t>customer_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>two_stars</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Two Stars</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>migration_type_choices</t>
+          <t>customer_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>internal</t>
+          <t>one_star</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>One Star</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
     </row>
@@ -1325,29 +1072,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>external</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>External</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>migration_status_choices</t>
+          <t>migration_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1376,148 +1123,182 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>customer_satisfaction_rating_choices</t>
+          <t>migration_status_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>five_stars</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Five Stars</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>customer_satisfaction_rating_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>four_prophets</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Four prophets</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>customer_satisfaction_rating_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>three_stars</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Three Stars</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>customer_satisfaction_rating_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>two_stars</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Two Stars</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>customer_satisfaction_rating_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>one_star</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>One Star</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>migration_type_choices</t>
+          <t>customer_satisfaction_rating_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>internal</t>
+          <t>five_stars</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Five Stars</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>migration_type_choices</t>
+          <t>customer_satisfaction_rating_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>four_stars</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Four Stars</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>migration_type_choices</t>
+          <t>customer_satisfaction_rating_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>three_stars</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Three Stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>customer_satisfaction_rating_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>two_stars</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Two Stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>customer_satisfaction_rating_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>one_star</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>One Star</t>
         </is>
       </c>
     </row>
